--- a/data/evaluation/benchmark_results.xlsx
+++ b/data/evaluation/benchmark_results.xlsx
@@ -1261,10 +1261,10 @@
         </is>
       </c>
       <c r="F12" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>2</v>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>NEWS_015</t>
+          <t>NEWS_015; NEWS_024; NEWS_025</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>待观察（建设中）</t>
+          <t>成功（已投产并转为全本地生产）</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>待观察（计划阶段）</t>
+          <t>待观察（计划阶段；投资金额需拆分核实）</t>
         </is>
       </c>
     </row>
@@ -1576,7 +1576,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>局部回流（未完全放弃印度）</t>
+          <t>工程团队撤回（订单/产能回流中国为待验证推断，未完全放弃印度）</t>
         </is>
       </c>
     </row>

--- a/data/evaluation/benchmark_results.xlsx
+++ b/data/evaluation/benchmark_results.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Case Results'!$A$1:$P$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Case Results'!$A$1:$N$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,25 +431,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P18"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="32" customWidth="1" min="11" max="11"/>
-    <col width="34" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
-    <col width="26" customWidth="1" min="16" max="16"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="42" customWidth="1" min="13" max="13"/>
+    <col width="26" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -470,65 +468,55 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>case_type</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>decision_problem</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>case_doc_id</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>case_doc_rank_baseline</t>
+          <t>benchmark_held_out</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>case_doc_rank_optimized</t>
+          <t>expected_decision_type</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>company_docs_in_corpus</t>
+          <t>evidence_index_ids</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>company_docs_retrieved</t>
+          <t>expected_risks</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>company_doc_recall</t>
+          <t>risks_identified_baseline</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>expected_risks</t>
+          <t>risk_recall_baseline</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>risks_identified_baseline</t>
+          <t>risk_recall_optimized</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>risk_recall_baseline</t>
+          <t>policy_evidence_top5_baseline</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>risk_recall_optimized</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>source_articles</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>verdict</t>
         </is>
@@ -552,53 +540,51 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
+          <t>China → Southeast Asia relocation</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
           <t>比亚迪 正在评估将部分产能从中国转移至泰国。管理层应基于现有证据判断该决策的风险。</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>RELOC_001</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>2</v>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>是（未进入 RAG 语料）</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>多地区混合布局</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>NEWS_001</t>
+        </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>PLUS1_003; RELOC_001</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
           <t>Market Access Risk; Political Risk; Trade Risk</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>Operational Risk; Supply Chain Risk</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>NEWS_001</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>TRD_001; MOFCOM_001; TRD_003; CASE_004; CASE_001</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>成功（本地供应链仍依赖中国）</t>
         </is>
@@ -622,53 +608,51 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
+          <t>China → Southeast Asia relocation</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
           <t>长安汽车 正在评估将部分产能从中国转移至泰国。管理层应基于现有证据判断该决策的风险。</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>RELOC_002</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>是（未进入 RAG 语料）</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>多地区混合布局</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>NEWS_002; COMPANY_REPORT_001</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Operational Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="L3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>RELOC_002</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>Market Access Risk; Operational Risk; Trade Risk</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>Operational Risk; Supply Chain Risk</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="N3" s="2" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>NEWS_002; COMPANY_REPORT_001</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>TRD_001; MOFCOM_001; TRD_003; CASE_004; CASE_001</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>成功（早期，产能爬坡中）</t>
         </is>
@@ -692,53 +676,51 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>China → Southeast Asia relocation</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>国轩高科 正在评估将部分产能从中国转移至越南。管理层应基于现有证据判断该决策的风险。</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>RELOC_003</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="n">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>是（未进入 RAG 语料）</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>多地区混合布局</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>NEWS_003; NEWS_004</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="L4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>RELOC_003</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>Market Access Risk; Supply Chain Risk; Trade Risk</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>Operational Risk; Supply Chain Risk</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="N4" s="2" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>NEWS_003; NEWS_004</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>TRD_001; TRD_003; MOFCOM_001; CASE_001; CASE_008</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>成功（材料端仍依赖中国）</t>
         </is>
@@ -762,53 +744,51 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>China → Southeast Asia relocation</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>亿纬锂能 正在评估将部分产能从中国转移至马来西亚。管理层应基于现有证据判断该决策的风险。</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>RELOC_004</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="n">
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>是（未进入 RAG 语料）</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>多地区混合布局</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>NEWS_005</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="L5" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>RELOC_004</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>NEWS_005</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>TRD_001; TRD_003; CASE_007; MOFCOM_001; CASE_001</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>成功（爬坡中）</t>
         </is>
@@ -832,53 +812,51 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>China → Southeast Asia relocation</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>欣旺达 正在评估将部分产能从中国转移至越南。管理层应基于现有证据判断该决策的风险。</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>RELOC_005</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="n">
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>是（未进入 RAG 语料）</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>多地区混合布局</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>NEWS_006; NEWS_007</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="L6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>RELOC_005</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>Operational Risk; Supply Chain Risk</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="N6" s="2" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>NEWS_006; NEWS_007</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>TRD_001; TRD_003; MOFCOM_001; CASE_001; CASE_008</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>待观察（尚未投产）</t>
         </is>
@@ -902,53 +880,51 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>China → Southeast Asia relocation</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>蜂巢能源 正在评估将部分产能从中国转移至泰国。管理层应基于现有证据判断该决策的风险。</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>RELOC_006</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>2</v>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>是（未进入 RAG 语料）</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>多地区混合布局</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>NEWS_008</t>
+        </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>RELOC_006; RETURN_004</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="n">
+          <t>Market Access Risk; Operational Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>Market Access Risk; Operational Risk; Trade Risk</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>Operational Risk; Supply Chain Risk</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="N7" s="2" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>NEWS_008</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>TRD_001; MOFCOM_001; TRD_003; CASE_001; CASE_004</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>成功（局部环节外移）</t>
         </is>
@@ -972,53 +948,51 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>China → Southeast Asia relocation</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>华友钴业 正在评估将部分产能从中国转移至印尼。管理层应基于现有证据判断该决策的风险。</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>RELOC_007</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>1</v>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>是（未进入 RAG 语料）</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>多地区混合布局</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>NEWS_009</t>
+        </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>RELOC_007</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
           <t>Political Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>Operational Risk; Supply Chain Risk</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="N8" s="2" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>NEWS_009</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_001; TRD_001; CASE_001; TRD_003; CASE_008</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>成功（上游外移，加工仍在国内）</t>
         </is>
@@ -1042,53 +1016,51 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>China → Southeast Asia relocation</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
           <t>中伟股份 正在评估将部分产能从中国转移至印尼。管理层应基于现有证据判断该决策的风险。</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>RELOC_008</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>1</v>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>是（未进入 RAG 语料）</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>多地区混合布局</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>NEWS_010; NEWS_011</t>
+        </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>RELOC_008</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
           <t>Operational Risk; Political Risk; Supply Chain Risk</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>Operational Risk; Supply Chain Risk</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="n">
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="n">
         <v>0.667</v>
       </c>
-      <c r="N9" s="2" t="n">
+      <c r="L9" s="2" t="n">
         <v>0.667</v>
       </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>NEWS_010; NEWS_011</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>TRD_001; MOFCOM_001; CASE_001; TRD_003; CASE_008</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>成功（上游外移）</t>
         </is>
@@ -1112,53 +1084,51 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>China + 1 strategy</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>宁德时代 正在推进 China+1 布局（匈牙利）。管理层应基于现有证据评估该布局的风险。</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>PLUS1_001</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>2</v>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>是（未进入 RAG 语料）</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>多地区混合布局</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>NEWS_012; NEWS_013</t>
+        </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>PLUS1_001; PLUS1_002</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
           <t>Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>Operational Risk; Supply Chain Risk</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>NEWS_012; NEWS_013</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Operational Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>CASE_010; CASE_008; CASE_001; CASE_004; CASE_007</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>待观察（试生产中，投资周期长）</t>
         </is>
@@ -1182,53 +1152,51 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>China + 1 strategy</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
           <t>宁德时代 正在推进 China+1 布局（印尼）。管理层应基于现有证据评估该布局的风险。</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>PLUS1_002</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>2</v>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>是（未进入 RAG 语料）</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>多地区混合布局</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>NEWS_014</t>
+        </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>PLUS1_001; PLUS1_002</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
           <t>Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>Operational Risk; Supply Chain Risk</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="N11" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>NEWS_014</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Operational Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>CASE_010; CASE_008; CASE_001; CASE_004; CASE_007</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>待观察（建设中）</t>
         </is>
@@ -1252,53 +1220,51 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>China + 1 strategy</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>比亚迪 正在推进 China+1 布局（印尼）。管理层应基于现有证据评估该布局的风险。</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>PLUS1_003</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="n">
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>是（未进入 RAG 语料）</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>多地区混合布局</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>NEWS_015; NEWS_024; NEWS_025</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Operational Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Operational Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G12" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>PLUS1_003; RELOC_001</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="n">
+      <c r="L12" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>Market Access Risk; Operational Risk; Trade Risk</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>Operational Risk; Supply Chain Risk</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="N12" s="2" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>NEWS_015; NEWS_024; NEWS_025</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>CASE_010; CASE_008; CASE_001; CASE_004; WH_002</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>成功（已投产并转为全本地生产）</t>
         </is>
@@ -1322,49 +1288,51 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>China + 1 strategy</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>晶科能源 正在推进 China+1 布局（马来西亚 / 越南 / 美国）。管理层应基于现有证据评估该布局的风险。</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>PLUS1_004</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>是（未进入 RAG 语料）</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>多地区混合布局</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>NEWS_016</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>Market Access Risk; Political Risk; Regulatory Risk; Trade Risk</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>Market Access Risk; Operational Risk; Supply Chain Risk; Trade Risk</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="n">
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="N13" s="2" t="n">
+      <c r="L13" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>NEWS_016</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>CASE_010; CASE_003; TRD_001; WH_002; TRD_003</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>成功（多地产能分散风险）</t>
         </is>
@@ -1388,53 +1356,51 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>China + 1 strategy</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>三星电子 正在推进 China+1 布局（韩国 / 越南）。管理层应基于现有证据评估该布局的风险。</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>PLUS1_005</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>1</v>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>是（未进入 RAG 语料）</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>多地区混合布局</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>NEWS_017</t>
+        </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>PLUS1_005</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
           <t>Operational Risk; Political Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>Operational Risk; Supply Chain Risk</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N14" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>NEWS_017</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Operational Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>CASE_010; CASE_001; CASE_008; TRD_003; TRD_001</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>待观察（计划阶段；投资金额需拆分核实）</t>
         </is>
@@ -1458,53 +1424,51 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>Reconsideration / Return to China</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
           <t>恩捷股份 正在重新评估海外布局，考虑提高中国生产比例、收缩海外新增产能。管理层应基于现有证据评估这一调整的风险。</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>RETURN_001</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="n">
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>是（未进入 RAG 语料）</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>提高中国生产比例</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>COMPANY_FILING_001; NEWS_018</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Operational Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G15" s="2" t="n">
+      <c r="L15" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>RETURN_001</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>Operational Risk; Supply Chain Risk</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="N15" s="2" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>COMPANY_FILING_001; NEWS_018</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>CASE_001; CASE_010; TRD_003; CASE_004; CASE_008</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>主动止损（成功止损，但海外布局目标未达成）</t>
         </is>
@@ -1528,53 +1492,51 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>Reconsideration / Return to China</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>富士康 正在重新评估海外布局，考虑提高中国生产比例、收缩海外新增产能。管理层应基于现有证据评估这一调整的风险。</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>RETURN_002</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>1</v>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>是（未进入 RAG 语料）</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>提高中国生产比例</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>NEWS_019; NEWS_020</t>
+        </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>RETURN_002</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
           <t>Operational Risk; Political Risk; Supply Chain Risk</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>Operational Risk; Supply Chain Risk</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="n">
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Operational Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="n">
         <v>0.667</v>
       </c>
-      <c r="N16" s="2" t="n">
+      <c r="L16" s="2" t="n">
         <v>0.667</v>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>NEWS_019; NEWS_020</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>CASE_001; CASE_010; TRD_003; CASE_004; CASE_008</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>工程团队撤回（订单/产能回流中国为待验证推断，未完全放弃印度）</t>
         </is>
@@ -1598,53 +1560,51 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>Reconsideration / Return to China</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>制造业外迁企业（行业层面） 正在重新评估海外布局，考虑提高中国生产比例、收缩海外新增产能。管理层应基于现有证据评估这一调整的风险。</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>RETURN_003</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>1</v>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>是（未进入 RAG 语料）</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>提高中国生产比例</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>REUTERS_001; NEWS_023</t>
+        </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>RETURN_003</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
           <t>Operational Risk; Political Risk; Supply Chain Risk</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>Operational Risk; Supply Chain Risk</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="n">
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Operational Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="n">
         <v>0.667</v>
       </c>
-      <c r="N17" s="2" t="n">
+      <c r="L17" s="2" t="n">
         <v>0.667</v>
       </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>REUTERS_001; NEWS_023</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>CASE_001; WH_002; TRD_003; CASE_010; CASE_008</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>行业性回流（结构性调整，非全面逆转）</t>
         </is>
@@ -1668,60 +1628,58 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>Reconsideration / Return to China</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>蜂巢能源 正在重新评估海外布局，考虑提高中国生产比例、收缩海外新增产能。管理层应基于现有证据评估这一调整的风险。</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>RETURN_004</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>2</v>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>是（未进入 RAG 语料）</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>维持现有海外布局（收缩新增）</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>NEWS_021; NEWS_022</t>
+        </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>RELOC_006; RETURN_004</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
           <t>Operational Risk; Political Risk; Trade Risk</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>Operational Risk; Supply Chain Risk</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="N18" s="2" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>NEWS_021; NEWS_022</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Operational Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>CASE_001; CASE_010; TRD_003; CASE_004; CASE_008</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>失败/主动退出（止损）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P18"/>
+  <autoFilter ref="A1:N18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1732,12 +1690,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="76" customWidth="1" min="3" max="3"/>
+    <col width="92" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1775,56 +1733,56 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>case-document recall@5</t>
+          <t>held out of the RAG corpus</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.9409999999999999</v>
+        <v>17</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>案例自己的语料文档是否进入 Top-5</t>
+          <t>17/17 案例仅供评测，不进入知识库（避免答案泄漏）</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>case-document recall@10</t>
+          <t>RAG corpus size</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.9409999999999999</v>
+        <v>30</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>同上，Top-10</t>
+          <t>语料只含 Task 1 证据，不含任何 benchmark 案例</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>company-document recall@10</t>
+          <t>risk recall (baseline)</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.779</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>该案例所属企业在语料中的所有文档被召回的比例</t>
+          <t>见 Task 6：期望风险中被检索证据覆盖的比例</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>risk recall (baseline)</t>
+          <t>risk recall (optimized)</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.461</v>
+        <v>0.779</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -1833,35 +1791,20 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>risk recall (optimized)</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>0.461</v>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>见 Task 6</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="n"/>
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" s="2" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n"/>
-      <c r="B8" s="2" t="n"/>
-      <c r="C8" s="2" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>口径说明</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr"/>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>案例绑定的 NEWS_* 是源文章（Task 5 Evidence Index），不在 RAG 语料中，因此不作为检索 gold；检索 gold 用案例自己在语料中的文档（= case_id）</t>
+      <c r="B8" s="2" t="inlineStr"/>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>本 benchmark 的案例是 held-out 答案键，故意不在 RAG 语料中，因此不再计算「案例文档召回」。检索层能力由 Task 2/3/4 评价，风险识别由 Task 6 评价；端到端「决策是否正确」需要 Agent 生成层，属下一阶段。</t>
         </is>
       </c>
     </row>

--- a/data/evaluation/benchmark_results.xlsx
+++ b/data/evaluation/benchmark_results.xlsx
@@ -581,7 +581,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>TRD_001; MOFCOM_001; TRD_003; CASE_004; CASE_001</t>
+          <t>EU_003; TRD_001; CASE_001; CASE_004; MOFCOM_001</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -645,11 +645,11 @@
         <v>1</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>TRD_001; MOFCOM_001; TRD_003; CASE_004; CASE_001</t>
+          <t>TRD_001; CASE_004; CASE_001; MOFCOM_001; TRD_003</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -713,11 +713,11 @@
         <v>1</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>TRD_001; TRD_003; MOFCOM_001; CASE_001; CASE_008</t>
+          <t>TRD_001; TRD_003; CASE_001; MOFCOM_001; CASE_008</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Operational Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="K5" s="2" t="n">
@@ -785,7 +785,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>TRD_001; TRD_003; CASE_007; MOFCOM_001; CASE_001</t>
+          <t>TRD_001; TRD_003; CASE_007; CASE_001; CASE_010</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>TRD_001; TRD_003; MOFCOM_001; CASE_001; CASE_008</t>
+          <t>TRD_001; TRD_003; CASE_001; MOFCOM_001; CASE_008</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -917,11 +917,11 @@
         <v>1</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>TRD_001; MOFCOM_001; TRD_003; CASE_001; CASE_004</t>
+          <t>TRD_001; CASE_004; CASE_001; MOFCOM_001; TRD_003</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>MOFCOM_001; TRD_001; CASE_001; TRD_003; CASE_008</t>
+          <t>TRD_001; CASE_001; MOFCOM_001; CASE_008; CASE_004</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>TRD_001; MOFCOM_001; CASE_001; TRD_003; CASE_008</t>
+          <t>TRD_001; CASE_001; MOFCOM_001; CASE_008; CASE_004</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>CASE_010; CASE_008; CASE_001; CASE_004; WH_002</t>
+          <t>CASE_010; CASE_008; CASE_001; CASE_004; EU_003</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Operational Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="K13" s="2" t="n">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>CASE_010; CASE_003; TRD_001; WH_002; TRD_003</t>
+          <t>CASE_010; CASE_003; TRD_001; CASE_007; WH_002</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>CASE_010; CASE_001; CASE_008; TRD_003; TRD_001</t>
+          <t>CASE_010; CASE_008; CASE_001; CASE_003; CASE_004</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; CASE_010; TRD_003; CASE_004; CASE_008</t>
+          <t>CASE_001; CASE_010; CASE_008; CASE_004; EU_003</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1522,18 +1522,18 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Operational Risk; Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0.667</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; CASE_010; TRD_003; CASE_004; CASE_008</t>
+          <t>CASE_001; CASE_010; CASE_008; CASE_004; CNGOV_001</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1590,18 +1590,18 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Operational Risk; Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0.667</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; WH_002; TRD_003; CASE_010; CASE_008</t>
+          <t>CASE_001; EU_003; CASE_010; CASE_008; CNGOV_001</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; CASE_010; TRD_003; CASE_004; CASE_008</t>
+          <t>CASE_001; CASE_010; CASE_008; CASE_004; EU_003</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1752,7 +1752,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.779</v>
+        <v>0.819</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.779</v>
+        <v>0.721</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>

--- a/data/evaluation/benchmark_results.xlsx
+++ b/data/evaluation/benchmark_results.xlsx
@@ -581,7 +581,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>EU_003; TRD_001; CASE_001; CASE_004; MOFCOM_001</t>
+          <t>SNE_001; TRD_001; EU_003; CASE_001; MOFCOM_001</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>TRD_001; CASE_004; CASE_001; MOFCOM_001; TRD_003</t>
+          <t>TRD_001; TRD_003; CASE_004; CASE_001; MOFCOM_001</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>TRD_001; TRD_003; CASE_001; MOFCOM_001; CASE_008</t>
+          <t>TRD_001; TRD_003; MOFCOM_001; CASE_001; WB_001</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="K5" s="2" t="n">
@@ -785,7 +785,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>TRD_001; TRD_003; CASE_007; CASE_001; CASE_010</t>
+          <t>TRD_001; TRD_003; CASE_007; WB_001; CASE_001</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>TRD_001; TRD_003; CASE_001; MOFCOM_001; CASE_008</t>
+          <t>TRD_001; TRD_003; MOFCOM_001; CASE_001; WB_001</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>TRD_001; CASE_004; CASE_001; MOFCOM_001; TRD_003</t>
+          <t>TRD_001; MOFCOM_001; CASE_001; CASE_004; TRD_003</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>TRD_001; CASE_001; MOFCOM_001; CASE_008; CASE_004</t>
+          <t>TRD_001; WB_001; MOFCOM_001; CASE_001; CASE_008</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>TRD_001; CASE_001; MOFCOM_001; CASE_008; CASE_004</t>
+          <t>TRD_001; WB_001; CASE_001; MOFCOM_001; CASE_008</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>CASE_010; CASE_008; CASE_001; CASE_004; CASE_007</t>
+          <t>SNE_001; CASE_010; CASE_001; CASE_008; WH_002</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>CASE_010; CASE_008; CASE_001; CASE_004; CASE_007</t>
+          <t>SNE_001; CASE_010; CASE_001; CASE_008; TSLA_001</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>CASE_010; CASE_008; CASE_001; CASE_004; EU_003</t>
+          <t>SNE_001; CASE_010; CASE_008; CASE_001; EU_003</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>CASE_010; CASE_003; TRD_001; CASE_007; WH_002</t>
+          <t>CASE_010; CASE_003; TRD_001; WH_002; CASE_007</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>CASE_010; CASE_008; CASE_001; CASE_003; CASE_004</t>
+          <t>CASE_010; CASE_008; CASE_001; CASE_003; SNE_001</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1454,18 +1454,18 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="K15" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; CASE_010; CASE_008; CASE_004; EU_003</t>
+          <t>CASE_001; DHS_001; CASE_008; CASE_004; EU_003</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1522,18 +1522,18 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="K16" s="2" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0.667</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; CASE_010; CASE_008; CASE_004; CNGOV_001</t>
+          <t>DHS_001; CASE_001; CASE_008; CASE_004; EU_003</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1590,18 +1590,18 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="K17" s="2" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0.667</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; EU_003; CASE_010; CASE_008; CNGOV_001</t>
+          <t>CASE_001; DHS_001; EU_003; SNE_001; CASE_010</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1658,18 +1658,18 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="K18" s="2" t="n">
         <v>0.667</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>0.667</v>
+        <v>0.333</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; CASE_010; CASE_008; CASE_004; EU_003</t>
+          <t>CASE_001; DHS_001; CASE_008; CASE_004; EU_003</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1752,7 +1752,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.819</v>
+        <v>0.779</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.721</v>
+        <v>0.681</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>

--- a/data/evaluation/benchmark_results.xlsx
+++ b/data/evaluation/benchmark_results.xlsx
@@ -560,7 +560,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>NEWS_001</t>
+          <t>TRD_001; EU_003; IEA_001; CASE_004; WB_001</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>NEWS_002; COMPANY_REPORT_001</t>
+          <t>TRD_001; CASE_004; IEA_001; WB_001</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -696,7 +696,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>NEWS_003; NEWS_004</t>
+          <t>TRD_001; TRD_003; SNE_001; WB_001; CASE_007</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>NEWS_005</t>
+          <t>TRD_001; TRD_003; CASE_007; SNE_001; WB_001</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>NEWS_006; NEWS_007</t>
+          <t>TRD_001; TRD_003; CASE_007; SNE_001; WB_001</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>NEWS_008</t>
+          <t>TRD_001; CASE_004; EU_003; IEA_001; WB_001</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>NEWS_009</t>
+          <t>WTO_004; TRD_003; SNE_001; WB_001</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>NEWS_010; NEWS_011</t>
+          <t>WTO_004; TRD_003; SNE_001; WB_001</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>NEWS_012; NEWS_013</t>
+          <t>EU_003; EU_001; EU_004; EU_002; SNE_001; IEA_001</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>NEWS_014</t>
+          <t>WTO_004; TRD_003; SNE_001; IEA_001</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>NEWS_015; NEWS_024; NEWS_025</t>
+          <t>WTO_004; IEA_001; SNE_001; TRD_003; EU_003</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>NEWS_016</t>
+          <t>DOC_001; CASE_002; CASE_003; TRD_002</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>NEWS_017</t>
+          <t>UNCTAD_001; TRD_003; WB_001; IMF_001</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>COMPANY_FILING_001; NEWS_018</t>
+          <t>CASE_001; TRD_003; WB_001; SNE_001</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>NEWS_019; NEWS_020</t>
+          <t>UNCTAD_001; WTO_002; WTO_003; CASE_001</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>REUTERS_001; NEWS_023</t>
+          <t>CASE_001; WB_001; TRD_001; KPMG_001</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>NEWS_021; NEWS_022</t>
+          <t>EU_003; EU_001; EU_004; CASE_001</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">

--- a/data/evaluation/benchmark_results.xlsx
+++ b/data/evaluation/benchmark_results.xlsx
@@ -581,7 +581,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>SNE_001; TRD_001; EU_003; CASE_001; MOFCOM_001</t>
+          <t>SNE_001; EU_003; TRD_001; CASE_001; MOFCOM_001</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>TRD_001; TRD_003; CASE_004; CASE_001; MOFCOM_001</t>
+          <t>TRD_001; TRD_003; CASE_001; CASE_004; MOFCOM_001</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; DHS_001; CASE_008; CASE_004; EU_003</t>
+          <t>CASE_001; DHS_001; CASE_008; EU_003; SNE_001</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1522,18 +1522,18 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Operational Risk; Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0.667</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>DHS_001; CASE_001; CASE_008; CASE_004; EU_003</t>
+          <t>DHS_001; CASE_001; CASE_008; EU_003; CNGOV_001</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; DHS_001; CASE_008; CASE_004; EU_003</t>
+          <t>CASE_001; DHS_001; CASE_008; EU_003; SNE_001</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.779</v>
+        <v>0.799</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>

--- a/data/evaluation/benchmark_results.xlsx
+++ b/data/evaluation/benchmark_results.xlsx
@@ -570,18 +570,18 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Operational Risk; Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0.667</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>SNE_001; EU_003; TRD_001; CASE_001; MOFCOM_001</t>
+          <t>SNE_001; EU_003; TRD_001; MOFCOM_003; CASE_004</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Operational Risk; Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="K3" s="2" t="n">
@@ -649,7 +649,7 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>TRD_001; TRD_003; CASE_001; CASE_004; MOFCOM_001</t>
+          <t>TRD_001; MOFCOM_003; CASE_004; TRD_003; NIO_001</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -706,18 +706,18 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Operational Risk; Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="K4" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>TRD_001; TRD_003; MOFCOM_001; CASE_001; WB_001</t>
+          <t>MOFCOM_003; TRD_001; CASE_001; MOFCOM_001; TRD_003</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -774,18 +774,18 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="K5" s="2" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>1</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>TRD_001; TRD_003; CASE_007; WB_001; CASE_001</t>
+          <t>TRD_001; MOFCOM_004; MOFCOM_003; TRD_003; MOFCOM_006</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Operational Risk; Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="K6" s="2" t="n">
@@ -853,7 +853,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>TRD_001; TRD_003; MOFCOM_001; CASE_001; WB_001</t>
+          <t>MOFCOM_003; TRD_001; MOFCOM_005; CASE_001; TRD_003</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -910,18 +910,18 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Operational Risk; Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="K7" s="2" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0.667</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>TRD_001; MOFCOM_001; CASE_001; CASE_004; TRD_003</t>
+          <t>TRD_001; MOFCOM_003; CASE_004; MOFCOM_004; CASE_001</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -978,18 +978,18 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Operational Risk; Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0.667</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>TRD_001; WB_001; MOFCOM_001; CASE_001; CASE_008</t>
+          <t>MOFCOM_003; TRD_001; WB_001; CASE_001; CASE_008</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1046,18 +1046,18 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Operational Risk; Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0.667</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>TRD_001; WB_001; CASE_001; MOFCOM_001; CASE_008</t>
+          <t>MOFCOM_003; TRD_001; WB_001; CASE_001; CASE_008</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>SNE_001; CASE_010; CASE_001; CASE_008; WH_002</t>
+          <t>SNE_001; CASE_010; CASE_008; CASE_001; CASE_002</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>SNE_001; CASE_010; CASE_001; CASE_008; TSLA_001</t>
+          <t>SNE_001; CASE_010; CASE_008; CASE_001; CASE_002</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>SNE_001; CASE_010; CASE_008; CASE_001; EU_003</t>
+          <t>SNE_001; CASE_010; EU_003; CASE_008; CASE_001</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1318,18 +1318,18 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Operational Risk; Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>CASE_010; CASE_003; TRD_001; WH_002; CASE_007</t>
+          <t>CASE_010; CASE_003; MOFCOM_004; CASE_007; TRD_001</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>CASE_010; CASE_008; CASE_001; CASE_003; SNE_001</t>
+          <t>CASE_010; CASE_008; CASE_001; TSLA_001; SNE_001</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Operational Risk; Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="K15" s="2" t="n">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; DHS_001; CASE_008; EU_003; SNE_001</t>
+          <t>DHS_001; CASE_001; MOFCOM_005; EU_003; CASE_008</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>DHS_001; CASE_001; CASE_008; EU_003; CNGOV_001</t>
+          <t>DHS_001; CASE_001; MOFCOM_005; EU_003; CASE_008</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1590,18 +1590,18 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Operational Risk; Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0.667</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; DHS_001; EU_003; SNE_001; CASE_010</t>
+          <t>CASE_001; DHS_001; MOFCOM_004; MOFCOM_005; EU_003</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1658,18 +1658,18 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Operational Risk; Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0.333</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; DHS_001; CASE_008; EU_003; SNE_001</t>
+          <t>DHS_001; CASE_001; MOFCOM_005; EU_003; CASE_008</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1752,7 +1752,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.799</v>
+        <v>0.887</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.681</v>
+        <v>0.701</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
